--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260611.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260611.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>12.44%</t>
+          <t>12.95%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.43%</t>
+          <t>10.12%</t>
         </is>
       </c>
     </row>
@@ -660,51 +660,51 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.79%</t>
+          <t>6.60%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>力成科技</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>1,764,000</t>
+          <t>22,138,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.63%</t>
+          <t>5.62%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>力成科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>22,138,000</t>
+          <t>1,764,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.18%</t>
+          <t>5.60%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.29%</t>
+          <t>4.40%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>2.97%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>2.94%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>2.71%</t>
         </is>
       </c>
     </row>
@@ -836,68 +836,68 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.63%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>14,717,000</t>
+          <t>19,558,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.41%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>2,827,000</t>
+          <t>14,334,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.35%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>14,334,000</t>
+          <t>14,717,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,105 +909,105 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>19,558,000</t>
+          <t>2,827,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>台灣積體</t>
+          <t>矽格股份</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>1,101,000</t>
+          <t>12,063,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.89%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>仁寶電腦</t>
+          <t>台灣積體</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>66,656,000</t>
+          <t>1,101,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.89%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>矽格股份</t>
+          <t>仁寶電腦</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>12,063,000</t>
+          <t>66,656,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.84%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>和碩聯合</t>
+          <t>宏碁股份</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>23,608,000</t>
+          <t>61,597,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>宏碁股份</t>
+          <t>和碩聯合</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>61,597,000</t>
+          <t>23,608,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,44 +1041,44 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>19,861,000</t>
+          <t>14,856,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>14,856,000</t>
+          <t>19,861,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
@@ -1100,117 +1100,117 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>1,807,102,346</t>
+          <t>20,131,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>日電貿股</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>20,131,000</t>
+          <t>7,181,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>頎邦科技</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>6,921,000</t>
+          <t>7,631,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>頎邦科技</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>7,631,000</t>
+          <t>6,921,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>日電貿股</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>7,181,000</t>
+          <t>1,512,548,765</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -1342,51 +1342,51 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>29,406,000</t>
+          <t>861,416,462</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.66%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>866,152,462</t>
+          <t>29,406,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.66%</t>
         </is>
       </c>
     </row>
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>神基控股</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>6,222,000</t>
+          <t>3,412,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>神基控股</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>3,412,000</t>
+          <t>6,222,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,44 +1459,44 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>6188</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>廣明光電</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>7,462,000</t>
+          <t>4,075,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>6188</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>廣明光電</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>4,075,000</t>
+          <t>7,462,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.23%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-336,714,834</t>
+          <t>-42,161,253</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-0.03%</t>
         </is>
       </c>
     </row>
